--- a/StructureDefinition-family-role.xlsx
+++ b/StructureDefinition-family-role.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T23:53:55+00:00</t>
+    <t>2025-12-03T18:37:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-family-role.xlsx
+++ b/StructureDefinition-family-role.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Study Family Focus</t>
+    <t>Family Role</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T18:37:31+00:00</t>
+    <t>2025-12-03T22:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>NCPI FHIR Working Group (http://example.org/example-publisher, ncpi-fhir-ig@googlegroups.com)</t>
+    <t>NCPI FHIR Working Group (https://www.ncpi-acc.org/about/working-groups, ncpi-fhir-ig@googlegroups.com)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -341,7 +341,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-FamilyMember</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-FamilyMember|3.0.0</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -683,7 +683,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.47265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.0" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-family-role.xlsx
+++ b/StructureDefinition-family-role.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Family Role</t>
+    <t>Study Family Focus</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T22:26:51+00:00</t>
+    <t>2026-01-13T18:03:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -341,7 +341,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-FamilyMember|3.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-FamilyMember</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -683,7 +683,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.0" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="43.47265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-family-role.xlsx
+++ b/StructureDefinition-family-role.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-13T18:03:13+00:00</t>
+    <t>2026-02-06T18:07:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-family-role.xlsx
+++ b/StructureDefinition-family-role.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Study Family Focus</t>
+    <t>Family Role</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T18:07:39+00:00</t>
+    <t>2026-03-09T20:11:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -341,7 +341,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-FamilyMember</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-FamilyMember|3.0.0</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -683,7 +683,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.47265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.0" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
